--- a/libertadores/datasets_liberta/confrontos_fase_3_libertadores.xlsx
+++ b/libertadores/datasets_liberta/confrontos_fase_3_libertadores.xlsx
@@ -495,7 +495,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -521,7 +521,7 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -547,7 +547,7 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
@@ -573,7 +573,7 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -599,7 +599,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -625,7 +625,7 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -651,7 +651,7 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
@@ -677,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
